--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBCC9EB-1A33-4E99-8FF4-40F665773907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008BABF7-D5E4-431C-8E03-F164152421CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,18 @@
   </si>
   <si>
     <t xml:space="preserve">revised the topic and read read book </t>
+  </si>
+  <si>
+    <t>had a discussion on mythology</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>I don’t konow what happened to me today , it to stressfull</t>
   </si>
 </sst>
 </file>
@@ -1636,48 +1648,96 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B19" s="14">
+        <v>550</v>
+      </c>
+      <c r="C19" s="14">
+        <v>40</v>
+      </c>
+      <c r="D19" s="14">
+        <v>240</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>250</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>300</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>60</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>50</v>
+      </c>
+      <c r="D20" s="14">
+        <v>140</v>
+      </c>
+      <c r="E20" s="14">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>300</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008BABF7-D5E4-431C-8E03-F164152421CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8A27CD-400A-4756-9A92-0FEE7CCB03B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,7 +268,10 @@
     <t>Very Unsatisfied</t>
   </si>
   <si>
-    <t>I don’t konow what happened to me today , it to stressfull</t>
+    <t>I don’t know what happened to me today , it to stressfull</t>
+  </si>
+  <si>
+    <t>I studied little bit , not focused</t>
   </si>
 </sst>
 </file>
@@ -1740,26 +1743,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
+      <c r="C21" s="14">
+        <v>50</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>20</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>400</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8A27CD-400A-4756-9A92-0FEE7CCB03B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6C6F56-C57C-4542-BA32-EDBE62AA19A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>I studied little bit , not focused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I don’t understand what I have done today , totally waste of time </t>
   </si>
 </sst>
 </file>
@@ -1788,27 +1791,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B22" s="14">
+        <v>500</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>500</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6C6F56-C57C-4542-BA32-EDBE62AA19A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814EF52F-A346-42D2-98E3-D0874A1547F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t xml:space="preserve">I don’t understand what I have done today , totally waste of time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">done little bit of coding  </t>
   </si>
 </sst>
 </file>
@@ -1838,26 +1841,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B23" s="14">
+        <v>450</v>
+      </c>
+      <c r="C23" s="14">
+        <v>40</v>
+      </c>
+      <c r="D23" s="14">
+        <v>240</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>500</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814EF52F-A346-42D2-98E3-D0874A1547F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD31830-7583-4068-9158-00DF421D680B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t xml:space="preserve">done little bit of coding  </t>
+  </si>
+  <si>
+    <t>read the news and learned little bit of basic c++</t>
   </si>
 </sst>
 </file>
@@ -1886,27 +1889,51 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B24" s="14">
+        <v>500</v>
+      </c>
+      <c r="C24" s="14">
+        <v>40</v>
+      </c>
+      <c r="D24" s="14">
+        <v>150</v>
+      </c>
+      <c r="E24" s="14">
+        <v>180</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>350</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>20</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD31830-7583-4068-9158-00DF421D680B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB357FC-8E29-4F79-BDE1-9612370033DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>read the news and learned little bit of basic c++</t>
+  </si>
+  <si>
+    <t>practiced question tought in the class today</t>
   </si>
 </sst>
 </file>
@@ -1891,7 +1894,7 @@
     </row>
     <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B24" s="14">
         <v>500</v>
@@ -1935,27 +1938,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>50</v>
+      </c>
+      <c r="D25" s="14">
+        <v>150</v>
+      </c>
+      <c r="E25" s="14">
+        <v>120</v>
+      </c>
+      <c r="F25" s="14">
+        <v>250</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>350</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB357FC-8E29-4F79-BDE1-9612370033DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD2AF36-8A65-45E6-8D27-8C09B043FF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>practiced question tought in the class today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not feeling good </t>
   </si>
 </sst>
 </file>
@@ -1985,26 +1988,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>50</v>
+      </c>
+      <c r="D26" s="14">
+        <v>100</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>250</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>500</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD2AF36-8A65-45E6-8D27-8C09B043FF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4E664-41E6-4DF6-BB6F-78EDFAC9F9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t xml:space="preserve">not feeling good </t>
+  </si>
+  <si>
+    <t xml:space="preserve">practiced sql </t>
   </si>
 </sst>
 </file>
@@ -2034,26 +2037,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>50</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4E664-41E6-4DF6-BB6F-78EDFAC9F9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7112B51-05D5-49E4-BEBD-3F678FA29781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t xml:space="preserve">practiced sql </t>
+  </si>
+  <si>
+    <t>learning c++</t>
   </si>
 </sst>
 </file>
@@ -2083,26 +2086,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="14">
+        <v>450</v>
+      </c>
+      <c r="C28" s="14">
+        <v>50</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>300</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7112B51-05D5-49E4-BEBD-3F678FA29781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4CD835-1B13-41F1-8959-C49826C1D043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>learning c++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revised the topic for ca and done little bit of coding </t>
   </si>
 </sst>
 </file>
@@ -2131,27 +2134,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B29" s="14">
+        <v>400</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>420</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>240</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4CD835-1B13-41F1-8959-C49826C1D043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435FCBE7-67AA-4518-B947-77205C3D10FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t xml:space="preserve">revised the topic for ca and done little bit of coding </t>
+  </si>
+  <si>
+    <t>studying for ca</t>
   </si>
 </sst>
 </file>
@@ -2181,26 +2184,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="14">
+        <v>400</v>
+      </c>
+      <c r="C30" s="14">
+        <v>40</v>
+      </c>
+      <c r="D30" s="14">
+        <v>540</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>350</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435FCBE7-67AA-4518-B947-77205C3D10FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA42E29E-2F47-41B5-A13A-0AB2CFDA31D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,9 +211,6 @@
     <t>Prakriti</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>D1P2635</t>
   </si>
   <si>
@@ -299,6 +296,12 @@
   </si>
   <si>
     <t>studying for ca</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning </t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1008,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1013,7 +1016,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1168,7 +1171,7 @@
         <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1208,13 +1211,13 @@
         <v>55</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1260,7 +1263,7 @@
         <v>51</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1306,7 +1309,7 @@
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1352,7 +1355,7 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1398,7 +1401,7 @@
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1441,10 +1444,10 @@
         <v>55</v>
       </c>
       <c r="M13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1484,13 +1487,13 @@
         <v>55</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1527,16 +1530,16 @@
         <v>280</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1582,7 +1585,7 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1625,10 +1628,10 @@
         <v>55</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1674,7 +1677,7 @@
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1720,7 +1723,7 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1757,16 +1760,16 @@
         <v>170</v>
       </c>
       <c r="K20" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L20" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="M20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>75</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1812,7 +1815,7 @@
         <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1852,13 +1855,13 @@
         <v>55</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1904,7 +1907,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1950,7 +1953,7 @@
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1987,16 +1990,16 @@
         <v>70</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2033,16 +2036,16 @@
         <v>140</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2088,7 +2091,7 @@
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2125,16 +2128,16 @@
         <v>110</v>
       </c>
       <c r="K28" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L28" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L28" s="16" t="s">
-        <v>75</v>
-      </c>
       <c r="M28" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2180,7 +2183,7 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2220,36 +2223,60 @@
         <v>55</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="14">
+        <v>450</v>
+      </c>
+      <c r="C31" s="14">
+        <v>40</v>
+      </c>
+      <c r="D31" s="14">
+        <v>60</v>
+      </c>
+      <c r="E31" s="14">
+        <v>180</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>450</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA42E29E-2F47-41B5-A13A-0AB2CFDA31D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A12E0F-B934-459E-9DA5-BEDC78AC38DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t xml:space="preserve">learning </t>
+  </si>
+  <si>
+    <t xml:space="preserve">practiced  code and studied for ca </t>
   </si>
 </sst>
 </file>
@@ -2278,27 +2281,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B32" s="14">
+        <v>500</v>
+      </c>
+      <c r="C32" s="14">
+        <v>40</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>360</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A12E0F-B934-459E-9DA5-BEDC78AC38DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFCFABD-3EAB-4727-A135-D835309CBFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t xml:space="preserve">practiced  code and studied for ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I started learning data analysis course </t>
   </si>
 </sst>
 </file>
@@ -2327,27 +2330,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="14">
+        <v>450</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>360</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFCFABD-3EAB-4727-A135-D835309CBFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3396E38-ECF1-4BAF-B137-F3C440B78611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t xml:space="preserve">I started learning data analysis course </t>
+  </si>
+  <si>
+    <t xml:space="preserve">not able to concentrate , watched movie </t>
   </si>
 </sst>
 </file>
@@ -2376,27 +2379,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B34" s="14">
+        <v>450</v>
+      </c>
+      <c r="C34" s="14">
+        <v>120</v>
+      </c>
+      <c r="D34" s="14">
+        <v>40</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>100</v>
+      </c>
+      <c r="G34" s="14">
+        <v>2</v>
+      </c>
+      <c r="H34" s="14">
+        <v>640</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3396E38-ECF1-4BAF-B137-F3C440B78611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B862D-FD34-4F73-9BFF-3D314432FBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t xml:space="preserve">not able to concentrate , watched movie </t>
+  </si>
+  <si>
+    <t>studied c++ and appitute  test</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1341,7 @@
         <v>60</v>
       </c>
       <c r="F11" s="14">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="G11" s="14">
         <v>6</v>
@@ -1348,11 +1351,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1330</v>
+        <v>1300</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>49</v>
@@ -1384,7 +1387,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="14">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="G12" s="14">
         <v>7</v>
@@ -1394,11 +1397,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>1290</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1430,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="14">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G13" s="14">
         <v>4</v>
@@ -1440,11 +1443,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1260</v>
+        <v>1010</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>430</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>55</v>
@@ -2426,26 +2429,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="14">
+        <v>450</v>
+      </c>
+      <c r="C35" s="14">
+        <v>40</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>350</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
@@ -10528,6 +10555,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B862D-FD34-4F73-9BFF-3D314432FBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD3F280-EE53-4DD8-96D0-A7E9B99A1E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>studied c++ and appitute  test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learning code and improving typing speed </t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1235,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>46250</v>
       </c>
@@ -1278,7 +1281,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>46251</v>
       </c>
@@ -2474,27 +2477,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="14">
+        <v>450</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>150</v>
+      </c>
+      <c r="E36" s="14">
+        <v>240</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>400</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
